--- a/data/college_admissions_registry.xlsx
+++ b/data/college_admissions_registry.xlsx
@@ -421,20 +421,20 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="60" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="43" customWidth="1" min="17" max="17"/>
     <col width="60" customWidth="1" min="18" max="18"/>
     <col width="18" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Кафедра</t>
+          <t>Бірлестік / кафедра</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Кафедра поступления</t>
+          <t>Бірлестік / кафедра (поступление)</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
@@ -570,57 +570,57 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>rjrrk ej'</t>
+          <t>grgrgrg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+77700042874</t>
+          <t>+77004287470</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Работник</t>
+          <t>Студент</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Инженерные технологии</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6B11380 - Вычислительная техника и программное обеспечение</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ВТПО 23-1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgIAAxkBAAIGvGn7UUKA5gNGUQydxGm3L9k9RY5AAAJnFGsbeLLYSyTzWVtJToM0AQADAgADeQADOwQ; server_path: data/files/5394280567/attestat_diplom.jpg</t>
+          <t>Telegram file_id: AgACAgIAAxkBAAIIxGoFjCjRzZHt7SFfs6nv_MzC40PdAAKzGGsbgoIxSAPfTcG6SA8-AQADAgADdwADOwQ; server_path: data/files/5394280567/attestat_diplom.jpg</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgIAAxkBAAIGvGn7UUKA5gNGUQydxGm3L9k9RY5AAAJnFGsbeLLYSyTzWVtJToM0AQADAgADeQADOwQ; server_path: data/files/5394280567/udostoverenie.jpg</t>
+          <t>Telegram file_id: AgACAgIAAxkBAAIIxGoFjCjRzZHt7SFfs6nv_MzC40PdAAKzGGsbgoIxSAPfTcG6SA8-AQADAgADdwADOwQ; server_path: data/files/5394280567/udostoverenie.jpg</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgIAAxkBAAIGvGn7UUKA5gNGUQydxGm3L9k9RY5AAAJnFGsbeLLYSyTzWVtJToM0AQADAgADeQADOwQ; server_path: data/files/5394280567/photo_3x4.jpg</t>
+          <t>Telegram file_id: AgACAgIAAxkBAAIIxGoFjCjRzZHt7SFfs6nv_MzC40PdAAKzGGsbgoIxSAPfTcG6SA8-AQADAgADdwADOwQ; server_path: data/files/5394280567/photo_3x4.jpg</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgIAAxkBAAIGvGn7UUKA5gNGUQydxGm3L9k9RY5AAAJnFGsbeLLYSyTzWVtJToM0AQADAgADeQADOwQ; server_path: data/files/5394280567/med_075u.jpg</t>
+          <t>Telegram file_id: AgACAgIAAxkBAAIIxGoFjCjRzZHt7SFfs6nv_MzC40PdAAKzGGsbgoIxSAPfTcG6SA8-AQADAgADdwADOwQ; server_path: data/files/5394280567/med_075u.jpg</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -630,17 +630,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>smi</t>
+          <t>аллала</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Технические и ИТ-направления</t>
+          <t>Бірлестік «Кәсіби-техникалық мамандықтар»</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>07151000 - Эксплуатация и ремонт полиграфического оборудования</t>
+          <t>02110500 — Технология полиграфического и упаковочного производства</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">

--- a/data/college_admissions_registry.xlsx
+++ b/data/college_admissions_registry.xlsx
@@ -48,8 +48,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,8 +420,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
@@ -434,8 +435,8 @@
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="43" customWidth="1" min="17" max="17"/>
-    <col width="60" customWidth="1" min="18" max="18"/>
+    <col width="49" customWidth="1" min="17" max="17"/>
+    <col width="31" customWidth="1" min="18" max="18"/>
     <col width="18" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
     <col width="26" customWidth="1" min="21" max="21"/>
@@ -556,26 +557,26 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5394280567</v>
+        <v>7939104831</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>spisoq</t>
+          <t>kotakbaser</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://t.me/spisoq</t>
+          <t>https://t.me/kotakbaser</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>grgrgrg</t>
+          <t>hdhdhdd</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+77004287470</t>
+          <t>+77003272517</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -605,22 +606,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgIAAxkBAAIIxGoFjCjRzZHt7SFfs6nv_MzC40PdAAKzGGsbgoIxSAPfTcG6SA8-AQADAgADdwADOwQ; server_path: data/files/5394280567/attestat_diplom.jpg</t>
+          <t>Telegram file_id: AgACAgQAAxkBAAIJNWoKD-56bOV54_DQllVKayJcp8MEAAK4DmsbQaxRUP2bQg-QJFKiAQADAgADdwADOwQ; server_path: data/files/7939104831/attestat_diplom.jpg</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgIAAxkBAAIIxGoFjCjRzZHt7SFfs6nv_MzC40PdAAKzGGsbgoIxSAPfTcG6SA8-AQADAgADdwADOwQ; server_path: data/files/5394280567/udostoverenie.jpg</t>
+          <t>Telegram file_id: AgACAgQAAxkBAAIJNWoKD-56bOV54_DQllVKayJcp8MEAAK4DmsbQaxRUP2bQg-QJFKiAQADAgADdwADOwQ; server_path: data/files/7939104831/udostoverenie.jpg</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgIAAxkBAAIIxGoFjCjRzZHt7SFfs6nv_MzC40PdAAKzGGsbgoIxSAPfTcG6SA8-AQADAgADdwADOwQ; server_path: data/files/5394280567/photo_3x4.jpg</t>
+          <t>Telegram file_id: AgACAgQAAxkBAAIJNWoKD-56bOV54_DQllVKayJcp8MEAAK4DmsbQaxRUP2bQg-QJFKiAQADAgADdwADOwQ; server_path: data/files/7939104831/photo_3x4.jpg</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgIAAxkBAAIIxGoFjCjRzZHt7SFfs6nv_MzC40PdAAKzGGsbgoIxSAPfTcG6SA8-AQADAgADdwADOwQ; server_path: data/files/5394280567/med_075u.jpg</t>
+          <t>Telegram file_id: AgACAgQAAxkBAAIJNWoKD-56bOV54_DQllVKayJcp8MEAAK4DmsbQaxRUP2bQg-QJFKiAQADAgADdwADOwQ; server_path: data/files/7939104831/med_075u.jpg</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -630,28 +631,28 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>аллала</t>
+          <t>dhjd</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Бірлестік «Кәсіби-техникалық мамандықтар»</t>
+          <t>Бірлестік «Қоғамдық - гуманитарлық мамандықтар»</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02110500 — Технология полиграфического и упаковочного производства</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+          <t>10130100 — Гостиничный бизнес</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="T2" t="n">
+      <c r="T2" s="1" t="n">
         <v>450000</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U2" s="1" t="n">
         <v>1800000</v>
       </c>
       <c r="V2" t="inlineStr">
